--- a/04_snowballing/full_text/full_text_selection.xlsx
+++ b/04_snowballing/full_text/full_text_selection.xlsx
@@ -75,10 +75,7 @@
     <t>http://dx.doi.org/10.5381/jot.2024.23.3.a5</t>
   </si>
   <si>
-    <t>Accepted</t>
-  </si>
-  <si>
-    <t>Studies that propose, analyze, or evaluate methods, techniques, approaches, tools, or frameworks for ACC.</t>
+    <t>Studies that are clearly misaligned with the research questions, even if they mention ACC-related terms.</t>
   </si>
   <si>
     <t>Backward</t>
@@ -109,9 +106,6 @@
   </si>
   <si>
     <t>https://doi.org/10.1007/s10270-022-01022-z</t>
-  </si>
-  <si>
-    <t>Studies that are clearly misaligned with the research questions, even if they mention ACC-related terms.</t>
   </si>
   <si>
     <t>UZUN, Burak; TEKINERDOGAN, Bedir. Detecting deviations in the code using architecture view-based drift analysis. Computer Standards &amp; Interfaces, v. 87, p. 103774, 2024.</t>
@@ -333,6 +327,9 @@
   </si>
   <si>
     <t>https://doi.org/10.1007/978-3-319-92901-9_8</t>
+  </si>
+  <si>
+    <t>Accepted</t>
   </si>
   <si>
     <t>Studies addressing ACC in microservice-based systems, including cloud-native and event-driven distributed architectures explicitly aligned with the microservices paradigm.</t>
@@ -844,6 +841,9 @@
   </si>
   <si>
     <t>https://doi.org/10.1002/spe.2974</t>
+  </si>
+  <si>
+    <t>Studies that propose, analyze, or evaluate methods, techniques, approaches, tools, or frameworks for ACC.</t>
   </si>
   <si>
     <t>J. Knodel, M. Naab, J. Knodel, and M. Naab, “How to perform the architecture compliance check (ace)? ” Pragmatic Evaluation of Software Architectures, pp. 83–94, 2016.</t>
@@ -1337,10 +1337,10 @@
         <v>19</v>
       </c>
       <c r="H3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I3" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="J3" s="5"/>
       <c r="K3" s="5"/>
@@ -1358,22 +1358,22 @@
         <v>1.0</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>21</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="G4" s="6" t="s">
         <v>26</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="H4" s="4" t="s">
         <v>14</v>
@@ -1400,23 +1400,23 @@
         <v>9</v>
       </c>
       <c r="C5" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>29</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>30</v>
       </c>
       <c r="F5" s="5"/>
       <c r="G5" s="6" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H5" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
@@ -1437,23 +1437,23 @@
         <v>9</v>
       </c>
       <c r="C6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E6" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>35</v>
       </c>
       <c r="F6" s="5"/>
       <c r="G6" s="8" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H6" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
@@ -1471,28 +1471,28 @@
         <v>1.0</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C7" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="F7" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="G7" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="H7" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I7" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="5"/>
@@ -1513,23 +1513,23 @@
         <v>9</v>
       </c>
       <c r="C8" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E8" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>44</v>
       </c>
       <c r="F8" s="5"/>
       <c r="G8" s="6" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="H8" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I8" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="5"/>
@@ -1547,28 +1547,28 @@
         <v>1.0</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="G9" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>50</v>
-      </c>
       <c r="H9" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I9" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="5"/>
@@ -1586,28 +1586,28 @@
         <v>1.0</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E10" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="F10" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="G10" s="8" t="s">
         <v>53</v>
       </c>
-      <c r="F10" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>55</v>
-      </c>
       <c r="H10" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I10" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="5"/>
@@ -1628,23 +1628,23 @@
         <v>9</v>
       </c>
       <c r="C11" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E11" s="4" t="s">
         <v>56</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>58</v>
       </c>
       <c r="F11" s="5"/>
       <c r="G11" s="6" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I11" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="5"/>
@@ -1662,28 +1662,28 @@
         <v>1.0</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="F12" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="G12" s="8" t="s">
         <v>62</v>
       </c>
-      <c r="F12" s="6" t="s">
-        <v>63</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>64</v>
-      </c>
       <c r="H12" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I12" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="5"/>
@@ -1704,23 +1704,23 @@
         <v>9</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E13" s="4" t="s">
         <v>65</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>67</v>
       </c>
       <c r="F13" s="5"/>
       <c r="G13" s="6" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I13" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="5"/>
@@ -1741,23 +1741,23 @@
         <v>9</v>
       </c>
       <c r="C14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="E14" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="F14" s="5"/>
       <c r="G14" s="6" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I14" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="5"/>
@@ -1778,23 +1778,23 @@
         <v>9</v>
       </c>
       <c r="C15" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="E15" s="4" t="s">
         <v>73</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>75</v>
       </c>
       <c r="F15" s="5"/>
       <c r="G15" s="8" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="5"/>
@@ -1812,28 +1812,28 @@
         <v>1.0</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C16" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="F16" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="G16" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>82</v>
-      </c>
       <c r="H16" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="5"/>
@@ -1851,28 +1851,28 @@
         <v>1.0</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C17" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E17" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="F17" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="G17" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="F17" s="8" t="s">
-        <v>86</v>
-      </c>
-      <c r="G17" s="8" t="s">
-        <v>87</v>
-      </c>
       <c r="H17" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I17" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="5"/>
@@ -1893,23 +1893,23 @@
         <v>9</v>
       </c>
       <c r="C18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E18" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E18" s="4" t="s">
-        <v>90</v>
       </c>
       <c r="F18" s="5"/>
       <c r="G18" s="6" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I18" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="5"/>
@@ -1927,26 +1927,26 @@
         <v>2.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>92</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>94</v>
       </c>
       <c r="F19" s="10"/>
       <c r="G19" s="11" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I19" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
@@ -1967,23 +1967,23 @@
         <v>9</v>
       </c>
       <c r="C20" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E20" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>98</v>
       </c>
       <c r="F20" s="10"/>
       <c r="G20" s="11" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I20" s="4" t="s">
         <v>99</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I20" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
@@ -2004,23 +2004,23 @@
         <v>9</v>
       </c>
       <c r="C21" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="E21" s="3" t="s">
         <v>102</v>
-      </c>
-      <c r="E21" s="3" t="s">
-        <v>103</v>
       </c>
       <c r="F21" s="10"/>
       <c r="G21" s="11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H21" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I21" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
@@ -2038,26 +2038,26 @@
         <v>2.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C22" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="3" t="s">
         <v>106</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>107</v>
       </c>
       <c r="F22" s="10"/>
       <c r="G22" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I22" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
@@ -2078,23 +2078,23 @@
         <v>9</v>
       </c>
       <c r="C23" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="3" t="s">
         <v>110</v>
-      </c>
-      <c r="E23" s="3" t="s">
-        <v>111</v>
       </c>
       <c r="F23" s="10"/>
       <c r="G23" s="11" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H23" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I23" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
@@ -2115,23 +2115,23 @@
         <v>9</v>
       </c>
       <c r="C24" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="D24" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="E24" s="3" t="s">
         <v>114</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>115</v>
       </c>
       <c r="F24" s="10"/>
       <c r="G24" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I24" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
@@ -2152,23 +2152,23 @@
         <v>9</v>
       </c>
       <c r="C25" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="E25" s="3" t="s">
         <v>118</v>
-      </c>
-      <c r="E25" s="3" t="s">
-        <v>119</v>
       </c>
       <c r="F25" s="10"/>
       <c r="G25" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I25" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
@@ -2186,26 +2186,26 @@
         <v>5.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C26" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="E26" s="3" t="s">
         <v>122</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>123</v>
       </c>
       <c r="F26" s="10"/>
       <c r="G26" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I26" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
@@ -2223,26 +2223,26 @@
         <v>5.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C27" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="3" t="s">
         <v>126</v>
-      </c>
-      <c r="E27" s="3" t="s">
-        <v>127</v>
       </c>
       <c r="F27" s="10"/>
       <c r="G27" s="11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H27" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I27" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
@@ -2260,26 +2260,26 @@
         <v>5.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C28" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="3" t="s">
         <v>130</v>
-      </c>
-      <c r="E28" s="3" t="s">
-        <v>131</v>
       </c>
       <c r="F28" s="10"/>
       <c r="G28" s="11" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H28" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I28" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
@@ -2297,24 +2297,24 @@
         <v>5.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C29" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D29" s="1" t="s">
         <v>133</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>134</v>
       </c>
       <c r="E29" s="1"/>
       <c r="F29" s="10"/>
       <c r="G29" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H29" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I29" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
@@ -2332,26 +2332,26 @@
         <v>5.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C30" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D30" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="E30" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="E30" s="3" t="s">
-        <v>138</v>
       </c>
       <c r="F30" s="10"/>
       <c r="G30" s="11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H30" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I30" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
@@ -2372,23 +2372,23 @@
         <v>9</v>
       </c>
       <c r="C31" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="D31" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="E31" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="E31" s="3" t="s">
-        <v>142</v>
       </c>
       <c r="F31" s="10"/>
       <c r="G31" s="11" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H31" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I31" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
@@ -2409,23 +2409,23 @@
         <v>9</v>
       </c>
       <c r="C32" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="E32" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E32" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="F32" s="10"/>
       <c r="G32" s="11" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H32" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I32" s="4" t="s">
         <v>20</v>
-      </c>
-      <c r="I32" s="4" t="s">
-        <v>100</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
@@ -2443,26 +2443,26 @@
         <v>7.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="D33" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="E33" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="E33" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="F33" s="10"/>
       <c r="G33" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H33" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I33" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
@@ -2480,26 +2480,26 @@
         <v>7.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>151</v>
+      </c>
+      <c r="D34" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="E34" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="E34" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="F34" s="10"/>
       <c r="G34" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H34" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I34" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
@@ -2520,23 +2520,23 @@
         <v>9</v>
       </c>
       <c r="C35" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="D35" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="E35" s="3" t="s">
         <v>157</v>
-      </c>
-      <c r="E35" s="3" t="s">
-        <v>158</v>
       </c>
       <c r="F35" s="10"/>
       <c r="G35" s="11" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H35" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I35" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
@@ -2557,23 +2557,23 @@
         <v>9</v>
       </c>
       <c r="C36" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="E36" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="F36" s="10"/>
       <c r="G36" s="11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H36" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I36" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
@@ -2591,26 +2591,26 @@
         <v>8.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C37" s="13" t="s">
+        <v>163</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="E37" s="3" t="s">
-        <v>166</v>
       </c>
       <c r="F37" s="10"/>
       <c r="G37" s="11" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I37" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
@@ -2631,23 +2631,23 @@
         <v>9</v>
       </c>
       <c r="C38" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="D38" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="E38" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="E38" s="3" t="s">
-        <v>170</v>
       </c>
       <c r="F38" s="10"/>
       <c r="G38" s="11" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I38" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
@@ -2665,26 +2665,26 @@
         <v>9.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C39" s="1" t="s">
+        <v>171</v>
+      </c>
+      <c r="D39" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="3" t="s">
         <v>173</v>
-      </c>
-      <c r="E39" s="3" t="s">
-        <v>174</v>
       </c>
       <c r="F39" s="10"/>
       <c r="G39" s="11" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H39" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I39" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
@@ -2705,23 +2705,23 @@
         <v>9</v>
       </c>
       <c r="C40" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="D40" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="E40" s="3" t="s">
         <v>177</v>
-      </c>
-      <c r="E40" s="3" t="s">
-        <v>178</v>
       </c>
       <c r="F40" s="10"/>
       <c r="G40" s="11" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H40" s="4" t="s">
-        <v>20</v>
+        <v>98</v>
       </c>
       <c r="I40" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
@@ -2739,26 +2739,26 @@
         <v>10.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C41" s="1" t="s">
+        <v>179</v>
+      </c>
+      <c r="D41" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="E41" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="E41" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="F41" s="10"/>
       <c r="G41" s="11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H41" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I41" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
@@ -2779,23 +2779,23 @@
         <v>9</v>
       </c>
       <c r="C42" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D42" s="2" t="s">
+      <c r="E42" s="3" t="s">
         <v>185</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>186</v>
       </c>
       <c r="F42" s="10"/>
       <c r="G42" s="11" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H42" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I42" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
@@ -2816,23 +2816,23 @@
         <v>9</v>
       </c>
       <c r="C43" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="D43" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D43" s="2" t="s">
+      <c r="E43" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="E43" s="3" t="s">
-        <v>190</v>
       </c>
       <c r="F43" s="10"/>
       <c r="G43" s="11" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H43" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I43" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
@@ -2853,23 +2853,23 @@
         <v>9</v>
       </c>
       <c r="C44" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="E44" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="F44" s="10"/>
       <c r="G44" s="11" t="s">
+        <v>194</v>
+      </c>
+      <c r="H44" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I44" s="4" t="s">
         <v>195</v>
-      </c>
-      <c r="H44" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I44" s="4" t="s">
-        <v>196</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
@@ -2890,23 +2890,23 @@
         <v>9</v>
       </c>
       <c r="C45" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="D45" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="D45" s="2" t="s">
+      <c r="E45" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="E45" s="3" t="s">
-        <v>199</v>
       </c>
       <c r="F45" s="10"/>
       <c r="G45" s="11" t="s">
+        <v>199</v>
+      </c>
+      <c r="H45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="I45" s="4" t="s">
         <v>200</v>
-      </c>
-      <c r="H45" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="I45" s="4" t="s">
-        <v>201</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
@@ -2924,26 +2924,26 @@
         <v>11.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C46" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="D46" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="E46" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="F46" s="10"/>
       <c r="G46" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H46" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I46" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="5"/>
@@ -2961,26 +2961,26 @@
         <v>12.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C47" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D47" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="E47" s="3" t="s">
         <v>207</v>
-      </c>
-      <c r="E47" s="3" t="s">
-        <v>208</v>
       </c>
       <c r="F47" s="10"/>
       <c r="G47" s="11" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H47" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I47" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="5"/>
@@ -3001,23 +3001,23 @@
         <v>9</v>
       </c>
       <c r="C48" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="D48" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="E48" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="E48" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="F48" s="10"/>
       <c r="G48" s="11" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H48" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I48" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="5"/>
@@ -3035,26 +3035,26 @@
         <v>18.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="D49" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="D49" s="2" t="s">
+      <c r="E49" s="3" t="s">
         <v>215</v>
-      </c>
-      <c r="E49" s="3" t="s">
-        <v>216</v>
       </c>
       <c r="F49" s="10"/>
       <c r="G49" s="11" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H49" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I49" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="5"/>
@@ -3072,26 +3072,26 @@
         <v>18.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="D50" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="E50" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="E50" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="F50" s="10"/>
       <c r="G50" s="11" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H50" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I50" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="5"/>
@@ -3109,26 +3109,26 @@
         <v>18.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>221</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="3" t="s">
         <v>223</v>
-      </c>
-      <c r="E51" s="3" t="s">
-        <v>224</v>
       </c>
       <c r="F51" s="10"/>
       <c r="G51" s="11" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H51" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I51" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="5"/>
@@ -3146,26 +3146,26 @@
         <v>19.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C52" s="1" t="s">
+        <v>225</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="E52" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="F52" s="10"/>
       <c r="G52" s="11" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H52" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I52" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="5"/>
@@ -3183,26 +3183,26 @@
         <v>19.0</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C53" s="1" t="s">
+        <v>229</v>
+      </c>
+      <c r="D53" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="E53" s="3" t="s">
         <v>231</v>
-      </c>
-      <c r="E53" s="3" t="s">
-        <v>232</v>
       </c>
       <c r="F53" s="10"/>
       <c r="G53" s="11" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H53" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I53" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="5"/>
@@ -3220,26 +3220,26 @@
         <v>19.0</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C54" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="D54" s="2" t="s">
+      <c r="E54" s="3" t="s">
         <v>235</v>
-      </c>
-      <c r="E54" s="3" t="s">
-        <v>236</v>
       </c>
       <c r="F54" s="10"/>
       <c r="G54" s="11" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H54" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I54" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="5"/>
@@ -3257,26 +3257,26 @@
         <v>19.0</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C55" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="D55" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="D55" s="2" t="s">
+      <c r="E55" s="3" t="s">
         <v>239</v>
-      </c>
-      <c r="E55" s="3" t="s">
-        <v>240</v>
       </c>
       <c r="F55" s="10"/>
       <c r="G55" s="11" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H55" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I55" s="4" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="5"/>
@@ -3294,26 +3294,26 @@
         <v>19.0</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C56" s="1" t="s">
+        <v>241</v>
+      </c>
+      <c r="D56" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D56" s="2" t="s">
+      <c r="E56" s="3" t="s">
         <v>243</v>
-      </c>
-      <c r="E56" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="F56" s="10"/>
       <c r="G56" s="11" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H56" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I56" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="5"/>
@@ -3331,26 +3331,26 @@
         <v>19.0</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C57" s="1" t="s">
+        <v>245</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="3" t="s">
         <v>247</v>
-      </c>
-      <c r="E57" s="3" t="s">
-        <v>248</v>
       </c>
       <c r="F57" s="10"/>
       <c r="G57" s="11" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H57" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I57" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="5"/>
@@ -3368,26 +3368,26 @@
         <v>19.0</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C58" s="1" t="s">
+        <v>249</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="3" t="s">
         <v>251</v>
-      </c>
-      <c r="E58" s="3" t="s">
-        <v>252</v>
       </c>
       <c r="F58" s="10"/>
       <c r="G58" s="11" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H58" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I58" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="5"/>
@@ -3405,26 +3405,26 @@
         <v>19.0</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C59" s="1" t="s">
+        <v>253</v>
+      </c>
+      <c r="D59" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="E59" s="3" t="s">
         <v>255</v>
-      </c>
-      <c r="E59" s="3" t="s">
-        <v>256</v>
       </c>
       <c r="F59" s="10"/>
       <c r="G59" s="11" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H59" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I59" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="5"/>
@@ -3442,26 +3442,26 @@
         <v>19.0</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>257</v>
+      </c>
+      <c r="D60" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="D60" s="2" t="s">
+      <c r="E60" s="3" t="s">
         <v>259</v>
-      </c>
-      <c r="E60" s="3" t="s">
-        <v>260</v>
       </c>
       <c r="F60" s="10"/>
       <c r="G60" s="11" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H60" s="4" t="s">
         <v>14</v>
       </c>
       <c r="I60" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="5"/>
@@ -3479,26 +3479,26 @@
         <v>21.0</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C61" s="1" t="s">
+        <v>261</v>
+      </c>
+      <c r="D61" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D61" s="2" t="s">
+      <c r="E61" s="3" t="s">
         <v>263</v>
-      </c>
-      <c r="E61" s="3" t="s">
-        <v>264</v>
       </c>
       <c r="F61" s="10"/>
       <c r="G61" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="H61" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>265</v>
-      </c>
-      <c r="H61" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="I61" s="4" t="s">
-        <v>21</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="5"/>
@@ -3516,7 +3516,7 @@
         <v>22.0</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C62" s="1" t="s">
         <v>266</v>
@@ -3535,7 +3535,7 @@
         <v>14</v>
       </c>
       <c r="I62" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J62" s="5"/>
       <c r="K62" s="5"/>
@@ -3572,7 +3572,7 @@
         <v>14</v>
       </c>
       <c r="I63" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J63" s="5"/>
       <c r="K63" s="5"/>
@@ -3590,7 +3590,7 @@
         <v>22.0</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C64" s="1" t="s">
         <v>274</v>
@@ -3609,7 +3609,7 @@
         <v>14</v>
       </c>
       <c r="I64" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J64" s="5"/>
       <c r="K64" s="5"/>
@@ -3627,7 +3627,7 @@
         <v>22.0</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C65" s="1" t="s">
         <v>278</v>
@@ -3646,7 +3646,7 @@
         <v>14</v>
       </c>
       <c r="I65" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J65" s="5"/>
       <c r="K65" s="5"/>
@@ -3664,7 +3664,7 @@
         <v>22.0</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C66" s="1" t="s">
         <v>282</v>
@@ -3683,7 +3683,7 @@
         <v>14</v>
       </c>
       <c r="I66" s="4" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
